--- a/save.xlsx
+++ b/save.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,29 +427,25 @@
           <t>model</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>batchsize</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NUDT-MIRSDT</t>
+          <t>IRDST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DQAligner</t>
+          <t>SDecNet</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>IRDST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DQAligner</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/save.xlsx
+++ b/save.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>NUDT-MIRSDT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>IRDST</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>SDecNet</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>4</v>
       </c>
     </row>

--- a/save.xlsx
+++ b/save.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,30 +436,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NUDT-MIRSDT</t>
+          <t>IRDST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SDecNet</t>
+          <t>STDecNet</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>IRDST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SDecNet</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
         <v>4</v>
       </c>
     </row>
